--- a/output/roomself_excel/11704.xlsx
+++ b/output/roomself_excel/11704.xlsx
@@ -498,10 +498,10 @@
         <v>2648</v>
       </c>
       <c r="E3" t="n">
-        <v>537</v>
+        <v>393</v>
       </c>
       <c r="F3" t="n">
-        <v>393</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4">
@@ -564,10 +564,10 @@
         <v>2064</v>
       </c>
       <c r="E6" t="n">
-        <v>537</v>
+        <v>300</v>
       </c>
       <c r="F6" t="n">
-        <v>300</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -589,7 +589,7 @@
         <v>575</v>
       </c>
       <c r="F7" t="n">
-        <v>532</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8">
@@ -630,10 +630,10 @@
         <v>3144</v>
       </c>
       <c r="E9" t="n">
-        <v>565</v>
+        <v>243</v>
       </c>
       <c r="F9" t="n">
-        <v>145</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">

--- a/output/roomself_excel/11704.xlsx
+++ b/output/roomself_excel/11704.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>1208</v>
       </c>
-      <c r="E2" t="n">
-        <v>202</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>156</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="G2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>124</v>
+      </c>
+      <c r="J2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,31 @@
       <c r="D3" t="n">
         <v>2648</v>
       </c>
-      <c r="E3" t="n">
-        <v>393</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>323</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="G3" t="n">
+        <v>32</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>361</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +592,38 @@
       <c r="D4" t="n">
         <v>3364</v>
       </c>
-      <c r="E4" t="n">
-        <v>532</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>385</v>
+        <v>486</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>355</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>355</v>
+      </c>
+      <c r="M4" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +641,23 @@
       <c r="D5" t="n">
         <v>1308</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>160</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>31</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +674,23 @@
       <c r="D6" t="n">
         <v>2064</v>
       </c>
-      <c r="E6" t="n">
-        <v>300</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>62</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +707,31 @@
       <c r="D7" t="n">
         <v>3132</v>
       </c>
-      <c r="E7" t="n">
-        <v>575</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>262</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="G7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>240</v>
+      </c>
+      <c r="J7" t="n">
+        <v>32</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +748,23 @@
       <c r="D8" t="n">
         <v>3100</v>
       </c>
-      <c r="E8" t="n">
-        <v>575</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>153</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="G8" t="n">
+        <v>24</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +781,23 @@
       <c r="D9" t="n">
         <v>3144</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>243</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>22</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +814,15 @@
       <c r="D10" t="n">
         <v>548</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +839,31 @@
       <c r="D11" t="n">
         <v>2580</v>
       </c>
-      <c r="E11" t="n">
-        <v>392</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>321</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="G11" t="n">
+        <v>24</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>368</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +880,31 @@
       <c r="D12" t="n">
         <v>1544</v>
       </c>
-      <c r="E12" t="n">
-        <v>311</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>131</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="G12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>109</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +921,23 @@
       <c r="D13" t="n">
         <v>932</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>106</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>32</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +954,31 @@
       <c r="D14" t="n">
         <v>984</v>
       </c>
-      <c r="E14" t="n">
-        <v>159</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>143</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="G14" t="n">
+        <v>24</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>119</v>
+      </c>
+      <c r="J14" t="n">
+        <v>32</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,11 +995,38 @@
       <c r="D15" t="n">
         <v>1900</v>
       </c>
-      <c r="E15" t="n">
-        <v>257</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>249</v>
+        <v>233</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>484</v>
+      </c>
+      <c r="J15" t="n">
+        <v>12</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>233</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
